--- a/AAII_Financials/Quarterly/QABSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QABSY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="92">
   <si>
     <t>QABSY</t>
   </si>
@@ -656,83 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -778,8 +786,14 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -825,8 +839,14 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -872,8 +892,14 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -891,8 +917,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -938,8 +966,14 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,8 +1019,14 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1032,8 +1072,14 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1079,8 +1125,14 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1095,8 +1147,10 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1142,8 +1196,14 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1189,8 +1249,14 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1208,8 +1274,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1255,8 +1323,14 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1302,8 +1376,14 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1349,8 +1429,14 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1396,8 +1482,14 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1443,8 +1535,14 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1490,8 +1588,14 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1537,8 +1641,14 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1584,8 +1694,14 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1631,8 +1747,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1678,8 +1800,14 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1725,8 +1853,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1772,8 +1906,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1819,8 +1959,14 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1866,8 +2012,14 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1913,8 +2065,14 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1960,60 +2118,72 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2031,8 +2201,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2050,63 +2222,71 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2265000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2247000</v>
+      </c>
+      <c r="F41" s="3">
         <v>1238000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1227600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1450900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1380200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1448100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1622400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1146300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1120300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1053200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>997000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2110500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>2126300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2817200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2670400</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -2115,10 +2295,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -2133,348 +2313,396 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>51900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>52300</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>870300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>863400</v>
+      </c>
+      <c r="F43" s="3">
         <v>677700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>672000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>799200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>760300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>625000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>700300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>770600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>753200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>808500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>765300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>702800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>708100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>740200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>701600</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>332800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>330100</v>
+      </c>
+      <c r="F44" s="3">
         <v>306800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>304300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>265500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>252600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>225900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>253100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>228800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>223700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>212700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>201300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>193000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>194500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>199100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>188800</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>261500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>259400</v>
+      </c>
+      <c r="F45" s="3">
         <v>413600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>410100</v>
       </c>
-      <c r="F45" s="3">
-        <v>444500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>422900</v>
-      </c>
       <c r="H45" s="3">
+        <v>163900</v>
+      </c>
+      <c r="I45" s="3">
+        <v>155900</v>
+      </c>
+      <c r="J45" s="3">
         <v>502500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>563000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>509100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>497600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>390600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>369700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>172400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>173700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>403700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>382700</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3950900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3919500</v>
+      </c>
+      <c r="F46" s="3">
         <v>2636100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2613900</v>
       </c>
-      <c r="F46" s="3">
-        <v>2960100</v>
-      </c>
-      <c r="G46" s="3">
-        <v>2815900</v>
-      </c>
       <c r="H46" s="3">
+        <v>2924700</v>
+      </c>
+      <c r="I46" s="3">
+        <v>2782200</v>
+      </c>
+      <c r="J46" s="3">
         <v>2801500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3138700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2654800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2594700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2464900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>2333400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3397700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>3423200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>4160300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>3943400</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>76800</v>
+      </c>
+      <c r="E47" s="3">
+        <v>76200</v>
+      </c>
+      <c r="F47" s="3">
         <v>32700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>32400</v>
       </c>
-      <c r="F47" s="3">
-        <v>29500</v>
-      </c>
-      <c r="G47" s="3">
-        <v>28100</v>
-      </c>
       <c r="H47" s="3">
+        <v>98300</v>
+      </c>
+      <c r="I47" s="3">
+        <v>93600</v>
+      </c>
+      <c r="J47" s="3">
         <v>28500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>31900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>26000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>25400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>23900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>22600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>83900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>84500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>15000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>14200</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11508800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>11417400</v>
+      </c>
+      <c r="F48" s="3">
         <v>12162500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>12060300</v>
       </c>
-      <c r="F48" s="3">
-        <v>11250200</v>
-      </c>
-      <c r="G48" s="3">
-        <v>10702300</v>
-      </c>
       <c r="H48" s="3">
+        <v>9400100</v>
+      </c>
+      <c r="I48" s="3">
+        <v>8942200</v>
+      </c>
+      <c r="J48" s="3">
         <v>9614500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>10771700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>9923300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>9698700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>9476500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>8970800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>7464200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>7520300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>7723100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>7320600</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>389500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>386400</v>
+      </c>
+      <c r="F49" s="3">
         <v>386900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>383600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>392100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>373000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>382400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>428500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>425700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>416000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>450600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>426500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>457200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>460700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>493400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>467700</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2520,8 +2748,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2567,55 +2801,67 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2693200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2671800</v>
+      </c>
+      <c r="F52" s="3">
         <v>692400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>686600</v>
       </c>
-      <c r="F52" s="3">
-        <v>653000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>621200</v>
-      </c>
       <c r="H52" s="3">
+        <v>2347700</v>
+      </c>
+      <c r="I52" s="3">
+        <v>2233400</v>
+      </c>
+      <c r="J52" s="3">
         <v>652900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>731500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>658500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>643600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>652400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>617500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1864900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1878900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>674200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>639100</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2661,55 +2907,67 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>18702200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>18553700</v>
+      </c>
+      <c r="F54" s="3">
         <v>15937800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>15804000</v>
       </c>
-      <c r="F54" s="3">
-        <v>15312400</v>
-      </c>
-      <c r="G54" s="3">
-        <v>14566500</v>
-      </c>
       <c r="H54" s="3">
+        <v>15190500</v>
+      </c>
+      <c r="I54" s="3">
+        <v>14450500</v>
+      </c>
+      <c r="J54" s="3">
         <v>13508300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>15134200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>13720300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>13409800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>13140400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>12439200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>13546800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>13648500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>13511900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>12807600</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2727,8 +2985,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2746,8 +3006,10 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2793,243 +3055,279 @@
       <c r="Q57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>626100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>621100</v>
+      </c>
+      <c r="F58" s="3">
         <v>591600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>586700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>421600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>401000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>383100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>429200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>400300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>391300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>450600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>426500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>918500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>925400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>861800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>816900</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7641600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>7581000</v>
+      </c>
+      <c r="F59" s="3">
         <v>7645400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>7581200</v>
       </c>
-      <c r="F59" s="3">
-        <v>7915200</v>
-      </c>
-      <c r="G59" s="3">
-        <v>7529600</v>
-      </c>
       <c r="H59" s="3">
+        <v>7015000</v>
+      </c>
+      <c r="I59" s="3">
+        <v>6673300</v>
+      </c>
+      <c r="J59" s="3">
         <v>6975700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>7815300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>7435300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>7267000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>6974100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>6601900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>6404000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>6452100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>6944900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>6582900</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9149800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>9077100</v>
+      </c>
+      <c r="F60" s="3">
         <v>8237100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>8167900</v>
       </c>
-      <c r="F60" s="3">
-        <v>8336700</v>
-      </c>
-      <c r="G60" s="3">
-        <v>7930600</v>
-      </c>
       <c r="H60" s="3">
+        <v>8301300</v>
+      </c>
+      <c r="I60" s="3">
+        <v>7897000</v>
+      </c>
+      <c r="J60" s="3">
         <v>7358700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>8244500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>7835600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>7658300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>7424700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>7028500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>8051200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>8111700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>7806700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>7399800</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6535500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6483600</v>
+      </c>
+      <c r="F61" s="3">
         <v>4905300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>4864100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>4794500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>4560900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>4090600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>4583000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>3997200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>3906700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>3721900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>3523300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>3558100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>3584800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>3623300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>3434500</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>429600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>426200</v>
+      </c>
+      <c r="F62" s="3">
         <v>443600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>439800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>367100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>349300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>342200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>383400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>304900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>298000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>526900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>498800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>593000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>597500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>704100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>667400</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3075,8 +3373,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3122,8 +3426,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3169,55 +3479,67 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17661700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>17521500</v>
+      </c>
+      <c r="F66" s="3">
         <v>15038000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>14911700</v>
       </c>
-      <c r="F66" s="3">
-        <v>14799100</v>
-      </c>
-      <c r="G66" s="3">
-        <v>14078200</v>
-      </c>
       <c r="H66" s="3">
+        <v>14677100</v>
+      </c>
+      <c r="I66" s="3">
+        <v>13962200</v>
+      </c>
+      <c r="J66" s="3">
         <v>13048500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>14619000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>13524200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>13218100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>13060700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>12363700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>13540100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>13641800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>13501000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>12797300</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3235,8 +3557,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3282,8 +3606,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3329,8 +3659,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3376,8 +3712,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3423,55 +3765,67 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>354900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>352100</v>
+      </c>
+      <c r="F72" s="3">
         <v>299500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>297000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-53100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-50500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-224600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-251700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-860700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-841200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-1000000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-946600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-1514100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-1525500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-2050600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-1943700</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3517,8 +3871,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3564,8 +3924,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3611,55 +3977,67 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1037000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1028800</v>
+      </c>
+      <c r="F76" s="3">
         <v>896500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>888900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>510100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>485200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>456700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>511700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>192800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>188500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>79100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>74900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>3300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>3400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>7500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3705,60 +4083,72 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3804,8 +4194,14 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3823,55 +4219,63 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>323200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>307500</v>
+      </c>
+      <c r="F83" s="3">
         <v>300800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>337000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>298900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>292100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>282200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>267100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>265200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>267200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>281400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>266700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>276300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>300800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>297800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>296600</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3917,8 +4321,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3964,8 +4374,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4011,8 +4427,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4058,8 +4480,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4105,55 +4533,67 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>740600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>734700</v>
+      </c>
+      <c r="F89" s="3">
         <v>584300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>579400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>714600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>679800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>641400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>718600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>700600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>684700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>457100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>432700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>756700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>762400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>955300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>905500</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4171,55 +4611,63 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-758600</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-752500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-634000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-628700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-818500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-778700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-439700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-492600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-442400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-432300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-489100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-463000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-625600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-630300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-242600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-230000</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4265,8 +4713,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4312,55 +4766,67 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-746800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-740900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-603300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-598300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-792300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-753700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-432000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-483900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-491400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-480300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-481900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-456200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-634900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-639700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-243700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-231000</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4378,29 +4844,31 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>155700</v>
+      </c>
+      <c r="E96" s="3">
+        <v>154400</v>
+      </c>
+      <c r="F96" s="3">
         <v>83400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>82700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>82000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>78000</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
@@ -4425,8 +4893,14 @@
       <c r="Q96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4472,8 +4946,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4519,8 +4999,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4566,145 +5052,169 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>501200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>497200</v>
+      </c>
+      <c r="F100" s="3">
         <v>-96400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-95600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>36100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>34300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-21000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-23600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-151100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-147700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-530700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-502400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-443300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-446600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-440400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-417500</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>4000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>4500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>1400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>1300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-2700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-2700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>1400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>1300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>1500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>490500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>486600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-119100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-118100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-41600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-39600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>192500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>215600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>57700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>56400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-554200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-524600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-324100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-326600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>272500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>258300</v>
       </c>
     </row>
